--- a/파이썬/코딩교실/2.코딩교실운영/줌다운/영상보내기.xlsx
+++ b/파이썬/코딩교실/2.코딩교실운영/줌다운/영상보내기.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Desktop\영상다운로드+링크발송\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실\2.코딩교실운영\줌다운\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC229CC1-0D58-4769-BF1E-5D5CA8D96C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F5F83C-4D0B-467F-9D2A-50A6331D8F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4308" yWindow="0" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -190,30 +195,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1I3kgwQE1FHylAZ_0TR343s3VI5CfoOVTwrVQ4XgXrKE/edit?gid=1066845978#gid=1066845978</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1vKYcNn3y7uV7uLFOyqXZfBL_8194avgXpBdNKVqVWWA/edit?gid=1066845978#gid=1066845978</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/u/0/folders/1_DjIKUqsvz7E32KDNL3FTeS7IH1Z6foS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/u/0/folders/1dPAMQHOBTvplyceJvifEiO91IjSFm_yR</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,6 +204,27 @@
   </si>
   <si>
     <t>https://docs.google.com/spreadsheets/d/1J2w-1sjSW7mcINdaUiLw1fVB_y8tOA4tiLTC1BU6iwo/edit?gid=1066845978#gid=1066845978</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1nywDE2DFzmm3BokXcUOW7goJLwYYX7uzN7zJS7sAi6A/edit?gid=1066845978#gid=1066845978</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1q0gqnyqYV27juUQKmNvL4ENpvUpxCUp2O-7QpfNiWUs/edit?gid=1066845978#gid=1066845978</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/11LBGZLWPOehuEqKnJjFbCTagleAMEDXh</t>
+  </si>
+  <si>
+    <t>포항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>북구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -405,9 +407,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -445,7 +447,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -551,7 +553,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -693,7 +695,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -781,10 +783,10 @@
         <v>22</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="S3"/>
       <c r="T3"/>
@@ -805,7 +807,7 @@
         <v>23</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="16.5" customHeight="1">
@@ -850,10 +852,10 @@
         <v>26</v>
       </c>
       <c r="Q7" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="16.5" customHeight="1">
@@ -868,7 +870,7 @@
         <v>27</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="16.5" customHeight="1">
@@ -883,7 +885,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="16.5" customHeight="1">
@@ -916,7 +918,7 @@
         <v>39</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="16.5" customHeight="1">
@@ -1015,14 +1017,11 @@
     <hyperlink ref="O2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="O1" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="Q13" r:id="rId4" xr:uid="{3CB9F841-DAA4-4181-B383-CF587203776D}"/>
-    <hyperlink ref="Q4" r:id="rId5" location="gid=1066845978" xr:uid="{FF2ABEDA-BA16-496E-8AB2-79785228E6CE}"/>
-    <hyperlink ref="Q3" r:id="rId6" location="gid=1066845978" xr:uid="{256E383A-B948-42C9-89AD-1F343418AA79}"/>
-    <hyperlink ref="Q5" r:id="rId7" xr:uid="{1B404A7C-1E14-4BBC-9769-CBEF269540BC}"/>
-    <hyperlink ref="Q9" r:id="rId8" xr:uid="{C887AF09-CCB2-4901-9316-1BCD2853710B}"/>
-    <hyperlink ref="Q7" r:id="rId9" location="gid=1066845978" xr:uid="{C980559A-1C01-4325-A46D-99001F4A4C64}"/>
-    <hyperlink ref="Q8" r:id="rId10" location="gid=1066845978" xr:uid="{4879EF0C-FD13-4955-B072-A27C2A0F8316}"/>
+    <hyperlink ref="Q9" r:id="rId5" xr:uid="{C887AF09-CCB2-4901-9316-1BCD2853710B}"/>
+    <hyperlink ref="Q7" r:id="rId6" location="gid=1066845978" xr:uid="{C980559A-1C01-4325-A46D-99001F4A4C64}"/>
+    <hyperlink ref="Q8" r:id="rId7" location="gid=1066845978" xr:uid="{4879EF0C-FD13-4955-B072-A27C2A0F8316}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>